--- a/testData/TestData.xlsx
+++ b/testData/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="6080" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Valid_Credentials" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Authorization_credentials" sheetId="4" r:id="rId3"/>
     <sheet name="SKU" sheetId="3" r:id="rId4"/>
     <sheet name="URL" sheetId="5" r:id="rId5"/>
+    <sheet name="CreateAccount" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>Email</t>
   </si>
@@ -76,6 +77,24 @@
   </si>
   <si>
     <t>https://staging.farmstore-modern.us/</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>EmailAddress</t>
+  </si>
+  <si>
+    <t>TestPlaywright</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Test1@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1413,4 +1432,54 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="20.8181818181818" customWidth="1"/>
+    <col min="3" max="3" width="22.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="15.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" display="Test1@yopmail.com"/>
+    <hyperlink ref="D2" r:id="rId2" display="Testing@123"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>